--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -456,296 +456,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KHI 6393 N</t>
+          <t>HI 32071 KB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-n/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-32071-kb/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Габариты (ВхШхГ)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>163х518х278</t>
-        </is>
-      </c>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>192х518х278</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KHI 6393 N</t>
+          <t>HI 32071 KB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-n/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-32071-kb/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KIT 0292 (в комплекте)</t>
-        </is>
-      </c>
+          <t>Цвет регуляторов</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KIT 0292</t>
+          <t>Черный</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KHI 6393 W</t>
+          <t>HI 43053 B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-w/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-43053-b/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Габариты (ВхШхГ)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>163х518х278</t>
-        </is>
-      </c>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>192х518х278</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KHI 6393 W</t>
+          <t>HI 43053 BW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-w/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-43053-bw/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KIT 0292 (в комплекте)</t>
-        </is>
-      </c>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>KIT 0292</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KHI 6393 X</t>
+          <t>HI 61071 KB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-x/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-61071-kb/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Габариты (ВхШхГ)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>163х518х278</t>
-        </is>
-      </c>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>192х518х278</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KHI 6393 X</t>
+          <t>HI 61071 KB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-x/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-61071-kb/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KIT 0292 (в комплекте)</t>
-        </is>
-      </c>
+          <t>Цвет регуляторов</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KIT 0292</t>
+          <t>Черный</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KHI 6788 GGR</t>
+          <t>HI 64560 BCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6788-ggr/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-64560-bch/</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KIT 0292 (в комплекте)</t>
-        </is>
-      </c>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KIT 0292</t>
+          <t>Да</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KHI 6788 GN</t>
+          <t>HIB 64870 BS Smart</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6788-gn/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-64870-bs-smart/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KIT 0292 (в комплекте)</t>
-        </is>
-      </c>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>KIT 0292</t>
+          <t>Да</t>
         </is>
       </c>
     </row>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,45 +456,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HI 32071 KB</t>
+          <t>KSFI 1997</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-32071-kb/</t>
+          <t>https://korting.ru/catalog/morozilnye-kamery/morozilnaya-kamera-ksfi-1997/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Варочные поверхности</t>
+          <t>Морозильные камеры</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>появился параметр</t>
+          <t>изменено</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Крепление фасада</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Слайдерное</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Жесткое</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HI 32071 KB</t>
+          <t>HIB 67010 HID M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-32071-kb/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-67010-hid-m/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,30 +508,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Цвет регуляторов</t>
-        </is>
-      </c>
+          <t>новая модель</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Черный</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HI 43053 B</t>
+          <t>HIB 97010 HID M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-43053-b/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-97010-hid-m/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -537,185 +533,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
+          <t>новая модель</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HI 43053 BW</t>
+          <t>OKB 9261 CPGN M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-43053-bw/</t>
+          <t>https://korting.ru/catalog/dukhovye-shkafy/elektricheskiy-dukhovoy-shkaf-okb-9261-cpgn-m/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Варочные поверхности</t>
+          <t>Духовые шкафы</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
+          <t>новая модель</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HI 61071 KB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-61071-kb/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Варочные поверхности</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HI 61071 KB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-61071-kb/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Варочные поверхности</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Цвет регуляторов</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Черный</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HI 64560 BCH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-64560-bch/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Варочные поверхности</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HIB 64870 BS Smart</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-64870-bs-smart/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Варочные поверхности</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>появился параметр</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KSFI 1997</t>
+          <t>KHI 6393 N</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/morozilnye-kamery/morozilnaya-kamera-ksfi-1997/</t>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-n/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Морозильные камеры</t>
+          <t>Вытяжки</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -476,94 +476,426 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Крепление фасада</t>
+          <t>Угольный фильтр</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Слайдерное</t>
+          <t>KIT 0292</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Жесткое</t>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HIB 67010 HID M</t>
+          <t>KHI 6393 W</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-67010-hid-m/</t>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-w/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Варочные поверхности</t>
+          <t>Вытяжки</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>новая модель</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KIT 0292</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HIB 97010 HID M</t>
+          <t>KHI 6393 X</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-97010-hid-m/</t>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-x/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Варочные поверхности</t>
+          <t>Вытяжки</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>новая модель</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KIT 0292</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OKB 9261 CPGN M</t>
+          <t>KHI 6788 GGR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/dukhovye-shkafy/elektricheskiy-dukhovoy-shkaf-okb-9261-cpgn-m/</t>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6788-ggr/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Духовые шкафы</t>
+          <t>Вытяжки</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>новая модель</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KIT 0292</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KHI 6788 GN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6788-gn/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KIT 0292</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KHP 6280 N</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6280-n/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KIT 0292 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KHP 6280 W</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6280-w/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KIT 0292 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KHP 6280 X</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6280-x/</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KIT 0292 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KHP 6704 GN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6704-gn/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KIT 0292 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KHP 6704 GW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6704-gw/</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KIT 0292 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIT 0292 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KHP 6900 DGN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6900-dgn/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KIT 0293 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KIT 0293 (Приобретаются отдельно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KHP 6900 DGW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6900-dgw/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Угольный фильтр</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KIT 0293 (2 шт. в комплекте)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KIT 0293 (Приобретаются отдельно)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,446 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KHI 6393 N</t>
+          <t>KMI 835 TGN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-n/</t>
+          <t>https://korting.ru/catalog/mikrovolnovye-pechi/mikrovolnovaya-pech-kmi-835-tgn/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Микроволновые печи</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>KIT 0292</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KHI 6393 W</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-w/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KIT 0292</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KHI 6393 X</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-x/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KIT 0292</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KHI 6788 GGR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6788-ggr/</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KIT 0292</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KHI 6788 GN</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6788-gn/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KIT 0292</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KHP 6280 N</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6280-n/</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KIT 0292 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KHP 6280 W</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6280-w/</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KIT 0292 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>KHP 6280 X</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6280-x/</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KIT 0292 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KHP 6704 GN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6704-gn/</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KIT 0292 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KHP 6704 GW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6704-gw/</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KIT 0292 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KIT 0292 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KHP 6900 DGN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6900-dgn/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KIT 0293 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KIT 0293 (Приобретаются отдельно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KHP 6900 DGW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/vytyazhka-s-vydvizhnym-ekranom-khp-6900-dgw/</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Угольный фильтр</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KIT 0293 (2 шт. в комплекте)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KIT 0293 (Приобретаются отдельно)</t>
-        </is>
-      </c>
+          <t>новая модель</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KMI 835 TGN</t>
+          <t>HIB 67010 HID M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/mikrovolnovye-pechi/mikrovolnovaya-pech-kmi-835-tgn/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-67010-hid-m/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Микроволновые печи</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>новая модель</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>появился параметр</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HIB 97010 HID M</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-97010-hid-m/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Варочные поверхности</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>появился параметр</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,66 +456,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HIB 67010 HID M</t>
+          <t>KHI 6393 N</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-67010-hid-m/</t>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-n/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Варочные поверхности</t>
+          <t>Вытяжки</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>появился параметр</t>
+          <t>изменено</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Номинальная потребляемая мощность</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HIB 97010 HID M</t>
+          <t>KHI 6393 W</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hib-97010-hid-m/</t>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-w/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Варочные поверхности</t>
+          <t>Вытяжки</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>появился параметр</t>
+          <t>изменено</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Постоянный нагрев</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Номинальная потребляемая мощность</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>128</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KHI 6393 X</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-x/</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Вытяжки</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>изменено</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Номинальная потребляемая мощность</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
     </row>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,111 +456,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KHI 6393 N</t>
+          <t>KD 60IHP83 GR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-n/</t>
+          <t>https://korting.ru/catalog/sushilnye-mashiny/sushilnaya-mashina-kd-60ihp83-gr/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Вытяжки</t>
+          <t>Сушильные машины</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>изменено</t>
+          <t>появился параметр</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Номинальная потребляемая мощность</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
+          <t>Слив конденсата</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KHI 6393 W</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-w/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Номинальная потребляемая мощность</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KHI 6393 X</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/vytyazhki/polnovstraivaemaya-vytyazhka-khi-6393-x/</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Вытяжки</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Номинальная потребляемая мощность</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>128</t>
+          <t>Контейнер/Водоотвод</t>
         </is>
       </c>
     </row>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -456,33 +456,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KD 60IHP83 GR</t>
+          <t>KWMT 1270 I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/sushilnye-mashiny/sushilnaya-mashina-kd-60ihp83-gr/</t>
+          <t>https://korting.ru/catalog/stiralnye-mashiny/stiralnaya-mashina-s-vertikalnoy-zagruzkoy-kwmt-1270-i/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Сушильные машины</t>
+          <t>Стиральные машины</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>появился параметр</t>
+          <t>изменено</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Слив конденсата</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Загрузка</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Контейнер/Водоотвод</t>
+          <t>7</t>
         </is>
       </c>
     </row>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,37 +456,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KWMT 1270 I</t>
+          <t>HI 60504 B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/stiralnye-mashiny/stiralnaya-mashina-s-vertikalnoy-zagruzkoy-kwmt-1270-i/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-60504-b/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Стиральные машины</t>
+          <t>Варочные поверхности</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>появился параметр</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Постоянный нагрев</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KD 60IHP83 GR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://korting.ru/catalog/sushilnye-mashiny/sushilnaya-mashina-kd-60ihp83-gr/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Сушильные машины</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>изменено</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Загрузка</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>7</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Слив конденсата</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Контейнер/Водоотвод</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Водоотвод</t>
         </is>
       </c>
     </row>

--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HI 60504 B</t>
+          <t>HI 30041 B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-60504-b/</t>
+          <t>https://korting.ru/catalog/varochnye-poverkhnosti/induktsionnaya-varochnaya-panel-hi-30041-b/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,43 +483,6 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>Да</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>KD 60IHP83 GR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://korting.ru/catalog/sushilnye-mashiny/sushilnaya-mashina-kd-60ihp83-gr/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Сушильные машины</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>изменено</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Слив конденсата</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Контейнер/Водоотвод</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Водоотвод</t>
         </is>
       </c>
     </row>
